--- a/artfynd/A 21205-2024 artfynd.xlsx
+++ b/artfynd/A 21205-2024 artfynd.xlsx
@@ -1188,7 +1188,7 @@
         <v>117873988</v>
       </c>
       <c r="B6" t="n">
-        <v>57721</v>
+        <v>57722</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
